--- a/10-razpredelnice/poraba.xlsx
+++ b/10-razpredelnice/poraba.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zalakmetic/Documents/fmf/1. letnik/1. semester/računalniški praktikum/racunalniski-praktikum/10-razpredelnice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25888FCD-ECBC-FC42-97DE-B4B700B4EA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C2A420-1458-F04B-8F7B-B9B9CCDE254F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15040" yWindow="680" windowWidth="14360" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15040" yWindow="680" windowWidth="14360" windowHeight="16640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Poraba" sheetId="4" r:id="rId1"/>
